--- a/DATA/ENGINEER SCHEDULES/SABER.xlsx
+++ b/DATA/ENGINEER SCHEDULES/SABER.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HHpro\DATA\ENGINEER SCHEDULES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84FD54D-5021-457A-9C10-474D26CACC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747ABAF7-E3AE-4822-995E-7CFBC84C880C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C267BFED-AA39-4284-8BDC-9CCD3F9CEB6D}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C267BFED-AA39-4284-8BDC-9CCD3F9CEB6D}"/>
   </bookViews>
   <sheets>
-    <sheet name="MULTI POSITION SPLITS" sheetId="1" r:id="rId1"/>
-    <sheet name="GAS RTU" sheetId="2" r:id="rId2"/>
+    <sheet name="MINI SPLITS" sheetId="3" r:id="rId1"/>
+    <sheet name="MULTI POSITION SPLITS" sheetId="1" r:id="rId2"/>
+    <sheet name="GAS RTU" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="98">
   <si>
     <t>SPLIT SYSTEM HEAT PUMP UNIT SCHEDULE</t>
   </si>
@@ -316,6 +317,57 @@
   </si>
   <si>
     <t>16.2 SEER2/12.2 EER2</t>
+  </si>
+  <si>
+    <t>IDU-1</t>
+  </si>
+  <si>
+    <t>IDU-2</t>
+  </si>
+  <si>
+    <t>DAIKIN
+FTXQ09ASBU9</t>
+  </si>
+  <si>
+    <t>DAIKIN
+FDMA18AVJU9</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>ODU-1</t>
+  </si>
+  <si>
+    <t>ODU-2</t>
+  </si>
+  <si>
+    <t>DAIKIN
+RXQ09ASBU9</t>
+  </si>
+  <si>
+    <t>DAIKIN
+RXP18AVJU9</t>
+  </si>
+  <si>
+    <t>115/1</t>
+  </si>
+  <si>
+    <t>18/59</t>
+  </si>
+  <si>
+    <t>82/127</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
+    <t>20.0 / 12.0 / 9.0 
+(SEER2/EER2/HSPF2)</t>
+  </si>
+  <si>
+    <t>18.0 / 11.6 / 9.2
+(SEER2/EER2/HSPF2)</t>
   </si>
 </sst>
 </file>
@@ -698,7 +750,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -709,11 +761,116 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -722,117 +879,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1169,6 +1215,575 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2617317-4666-441B-B6C3-2A8749A9C445}">
+  <dimension ref="C1:Y34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="11.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" style="1" customWidth="1"/>
+    <col min="6" max="13" width="9.140625" style="1"/>
+    <col min="14" max="14" width="10.7109375" style="1" customWidth="1"/>
+    <col min="15" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="16.5703125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.85546875" style="1" customWidth="1"/>
+    <col min="21" max="23" width="9.140625" style="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="37.28515625" style="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:25" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+    </row>
+    <row r="2" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+    </row>
+    <row r="3" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="36"/>
+      <c r="L3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" s="35"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="V3" s="35"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+    </row>
+    <row r="4" spans="3:25" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="3:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="C5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="8">
+        <v>424</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J5" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="K5" s="8">
+        <v>8.14</v>
+      </c>
+      <c r="L5" s="30">
+        <v>12</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R5" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="S5" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="T5" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="V5" s="8">
+        <v>14.9</v>
+      </c>
+      <c r="W5" s="8">
+        <v>15</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="3:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="11">
+        <v>609</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="29">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="K6" s="11">
+        <v>14.46</v>
+      </c>
+      <c r="L6" s="29">
+        <v>25</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="R6" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="S6" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="T6" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="V6" s="11">
+        <v>21.4</v>
+      </c>
+      <c r="W6" s="11">
+        <v>25</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y6" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C7" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="15"/>
+    </row>
+    <row r="8" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C8" s="16">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y8" s="17"/>
+    </row>
+    <row r="9" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C9" s="16">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y9" s="17"/>
+    </row>
+    <row r="10" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C10" s="16">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y10" s="17"/>
+    </row>
+    <row r="11" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C11" s="16">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y11" s="17"/>
+    </row>
+    <row r="12" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C12" s="16">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y12" s="17"/>
+    </row>
+    <row r="13" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C13" s="16">
+        <v>6</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y13" s="17"/>
+    </row>
+    <row r="14" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C14" s="16">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y14" s="17"/>
+    </row>
+    <row r="15" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C15" s="16">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y15" s="17"/>
+    </row>
+    <row r="16" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C16" s="16">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y16" s="17"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C17" s="16">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y17" s="17"/>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C18" s="16">
+        <v>11</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y18" s="17"/>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C19" s="16">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y19" s="17"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C20" s="16">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y20" s="17"/>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C21" s="16">
+        <v>14</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y21" s="17"/>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C22" s="16"/>
+      <c r="D22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y22" s="17"/>
+    </row>
+    <row r="23" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="18"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="21"/>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C24" s="3"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C25" s="3"/>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C26" s="3"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C27" s="3"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C28" s="3"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C29" s="3"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:Y1"/>
+    <mergeCell ref="C2:P2"/>
+    <mergeCell ref="Q2:W2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:W3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF58C68-F131-447B-B3D4-C9F7873870E1}">
   <dimension ref="C1:Y34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1217,770 +1832,470 @@
       <c r="Y1" s="33"/>
     </row>
     <row r="2" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="9" t="s">
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="9" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="9" t="s">
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="13" t="s">
+      <c r="K3" s="36"/>
+      <c r="L3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="10"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="9" t="s">
+      <c r="O3" s="35"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="9" t="s">
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="10"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="12"/>
-      <c r="Y3" s="12"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="3:25" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="14" t="s">
+      <c r="M4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="14" t="s">
+      <c r="N4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="14" t="s">
+      <c r="O4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="14" t="s">
+      <c r="P4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="14" t="s">
+      <c r="Q4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="R4" s="14" t="s">
+      <c r="R4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="T4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="U4" s="14" t="s">
+      <c r="U4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="V4" s="14" t="s">
+      <c r="V4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="W4" s="14" t="s">
+      <c r="W4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="X4" s="14" t="s">
+      <c r="X4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y4" s="13" t="s">
+      <c r="Y4" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="3:25" ht="30" x14ac:dyDescent="0.25">
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="8">
         <v>1600</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="8">
         <v>0.75</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="8">
         <v>46.1</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="8">
         <v>36.418999999999997</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="30">
         <v>46</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="8">
         <v>3</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O5" s="8">
         <v>20.7</v>
       </c>
-      <c r="P5" s="16">
+      <c r="P5" s="8">
         <v>25</v>
       </c>
-      <c r="Q5" s="16" t="s">
+      <c r="Q5" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="R5" s="42" t="s">
+      <c r="R5" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="S5" s="16">
+      <c r="S5" s="8">
         <v>4</v>
       </c>
-      <c r="T5" s="16" t="s">
+      <c r="T5" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="U5" s="16" t="s">
+      <c r="U5" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="V5" s="16">
+      <c r="V5" s="8">
         <v>25.5</v>
       </c>
-      <c r="W5" s="16">
+      <c r="W5" s="8">
         <v>40</v>
       </c>
-      <c r="X5" s="16" t="s">
+      <c r="X5" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="Y5" s="17" t="s">
+      <c r="Y5" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="3:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="11">
         <v>1380</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="11">
         <v>1</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="J6" s="44">
+      <c r="J6" s="29">
         <v>41</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="11">
         <v>29.52</v>
       </c>
-      <c r="L6" s="44">
+      <c r="L6" s="29">
         <v>41</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="11">
         <v>8</v>
       </c>
-      <c r="N6" s="19" t="s">
+      <c r="N6" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="11">
         <v>44.8</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="11">
         <v>45</v>
       </c>
-      <c r="Q6" s="19" t="s">
+      <c r="Q6" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="R6" s="43" t="s">
+      <c r="R6" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="S6" s="19">
+      <c r="S6" s="11">
         <v>3.5</v>
       </c>
-      <c r="T6" s="19" t="s">
+      <c r="T6" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="U6" s="19" t="s">
+      <c r="U6" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="V6" s="19">
+      <c r="V6" s="11">
         <v>37.5</v>
       </c>
-      <c r="W6" s="19">
+      <c r="W6" s="11">
         <v>40</v>
       </c>
-      <c r="X6" s="19" t="s">
+      <c r="X6" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="Y6" s="20" t="s">
+      <c r="Y6" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="23"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="15"/>
     </row>
     <row r="8" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C8" s="24">
+      <c r="C8" s="16">
         <v>1</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="25"/>
+      <c r="Y8" s="17"/>
     </row>
     <row r="9" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C9" s="24">
+      <c r="C9" s="16">
         <v>2</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="25"/>
+      <c r="Y9" s="17"/>
     </row>
     <row r="10" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C10" s="24">
+      <c r="C10" s="16">
         <v>3</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="25"/>
+      <c r="Y10" s="17"/>
     </row>
     <row r="11" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C11" s="24">
+      <c r="C11" s="16">
         <v>4</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="25"/>
+      <c r="Y11" s="17"/>
     </row>
     <row r="12" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C12" s="24">
+      <c r="C12" s="16">
         <v>5</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="25"/>
+      <c r="Y12" s="17"/>
     </row>
     <row r="13" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C13" s="24">
+      <c r="C13" s="16">
         <v>6</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="25"/>
+      <c r="Y13" s="17"/>
     </row>
     <row r="14" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C14" s="24">
+      <c r="C14" s="16">
         <v>7</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="25"/>
+      <c r="Y14" s="17"/>
     </row>
     <row r="15" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C15" s="24">
+      <c r="C15" s="16">
         <v>8</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="25"/>
+      <c r="Y15" s="17"/>
     </row>
     <row r="16" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C16" s="24">
+      <c r="C16" s="16">
         <v>9</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="25"/>
+      <c r="Y16" s="17"/>
     </row>
     <row r="17" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C17" s="24">
+      <c r="C17" s="16">
         <v>10</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="25"/>
+      <c r="Y17" s="17"/>
     </row>
     <row r="18" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C18" s="24">
+      <c r="C18" s="16">
         <v>11</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="25"/>
+      <c r="Y18" s="17"/>
     </row>
     <row r="19" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C19" s="24">
+      <c r="C19" s="16">
         <v>12</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="25"/>
+      <c r="Y19" s="17"/>
     </row>
     <row r="20" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C20" s="24">
+      <c r="C20" s="16">
         <v>13</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="25"/>
+      <c r="Y20" s="17"/>
     </row>
     <row r="21" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C21" s="24">
+      <c r="C21" s="16">
         <v>14</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="25"/>
+      <c r="Y21" s="17"/>
     </row>
     <row r="22" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="C22" s="24"/>
-      <c r="D22" s="4" t="s">
+      <c r="C22" s="16"/>
+      <c r="D22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="25"/>
+      <c r="Y22" s="17"/>
     </row>
     <row r="23" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="26"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="28"/>
-      <c r="Y23" s="29"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="21"/>
     </row>
     <row r="24" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C24" s="3"/>
@@ -2037,27 +2352,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52AB9156-2178-4C56-98F2-183E02A08758}">
   <dimension ref="B1:X40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="30"/>
-    <col min="3" max="3" width="12.140625" style="30" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" style="30" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" style="30"/>
-    <col min="7" max="7" width="14.42578125" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" style="30"/>
-    <col min="10" max="13" width="13" style="30" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" style="30" customWidth="1"/>
-    <col min="17" max="17" width="18.85546875" style="30" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" style="30" customWidth="1"/>
-    <col min="19" max="19" width="20" style="30" customWidth="1"/>
-    <col min="20" max="20" width="13.28515625" style="30" customWidth="1"/>
-    <col min="21" max="21" width="24.5703125" style="30" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="30"/>
+    <col min="1" max="2" width="9.140625" style="22"/>
+    <col min="3" max="3" width="12.140625" style="22" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" style="22" customWidth="1"/>
+    <col min="5" max="6" width="9.140625" style="22"/>
+    <col min="7" max="7" width="14.42578125" style="22" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="22"/>
+    <col min="10" max="13" width="13" style="22" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="22" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.140625" style="22" customWidth="1"/>
+    <col min="17" max="17" width="18.85546875" style="22" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" style="22" customWidth="1"/>
+    <col min="19" max="19" width="20" style="22" customWidth="1"/>
+    <col min="20" max="20" width="13.28515625" style="22" customWidth="1"/>
+    <col min="21" max="21" width="24.5703125" style="22" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:24" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -2084,518 +2399,518 @@
       <c r="U1" s="33"/>
     </row>
     <row r="2" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="6" t="s">
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="6" t="s">
+      <c r="K2" s="43"/>
+      <c r="L2" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="9" t="s">
+      <c r="M2" s="43"/>
+      <c r="N2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="34" t="s">
+      <c r="O2" s="35"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="35" t="s">
+      <c r="R2" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="35" t="s">
+      <c r="S2" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="34" t="s">
+      <c r="T2" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="U2" s="34" t="s">
+      <c r="U2" s="39" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="2:24" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37" t="s">
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="37" t="s">
+      <c r="K3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="37" t="s">
+      <c r="L3" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="38" t="s">
+      <c r="N3" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="O3" s="37" t="s">
+      <c r="O3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="37" t="s">
+      <c r="P3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
     </row>
     <row r="4" spans="2:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="8">
         <v>1265</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="8">
         <v>0.5</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="8">
         <v>1.2</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="8">
         <v>35.417999999999999</v>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="8">
         <v>27.395</v>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="8">
         <v>45</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="8">
         <v>36.450000000000003</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="N4" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="O4" s="16">
+      <c r="O4" s="8">
         <v>9.1</v>
       </c>
-      <c r="P4" s="16">
+      <c r="P4" s="8">
         <v>15</v>
       </c>
-      <c r="Q4" s="42" t="s">
+      <c r="Q4" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="16">
+      <c r="R4" s="8">
         <v>3</v>
       </c>
-      <c r="S4" s="16" t="s">
+      <c r="S4" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="T4" s="16">
+      <c r="T4" s="8">
         <v>520</v>
       </c>
-      <c r="U4" s="17" t="s">
+      <c r="U4" s="9" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="5" spans="2:24" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="11">
         <v>2100</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="11">
         <v>0.5</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="11">
         <v>1</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="11">
         <v>60.036999999999999</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="11">
         <v>46.024000000000001</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="11">
         <v>115</v>
       </c>
-      <c r="M5" s="19">
+      <c r="M5" s="11">
         <v>93.15</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="N5" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="11">
         <v>28.5</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="11">
         <v>40</v>
       </c>
-      <c r="Q5" s="43" t="s">
+      <c r="Q5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="11">
         <v>5</v>
       </c>
-      <c r="S5" s="19" t="s">
+      <c r="S5" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="T5" s="19">
+      <c r="T5" s="11">
         <v>655</v>
       </c>
-      <c r="U5" s="20" t="s">
+      <c r="U5" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="23"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="15"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
-      <c r="C7" s="24">
+      <c r="C7" s="16">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="25"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="17"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="24">
+      <c r="C8" s="16">
         <v>2</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="25"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="17"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
     </row>
     <row r="9" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="C9" s="24">
+      <c r="C9" s="16">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="25"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="17"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
-      <c r="C10" s="24">
+      <c r="C10" s="16">
         <v>4</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="25"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="17"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
-      <c r="C11" s="24">
+      <c r="C11" s="16">
         <v>5</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="25"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="17"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
     </row>
     <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
-      <c r="C12" s="24">
+      <c r="C12" s="16">
         <v>6</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="25"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="17"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
     </row>
     <row r="13" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
-      <c r="C13" s="24">
+      <c r="C13" s="16">
         <v>7</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="25"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="17"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
     </row>
     <row r="14" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
-      <c r="C14" s="24">
+      <c r="C14" s="16">
         <v>8</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="25"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="17"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
     </row>
     <row r="15" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="4" t="s">
+      <c r="C15" s="16"/>
+      <c r="D15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="25"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="17"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
     </row>
     <row r="16" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
-      <c r="U16" s="29"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="21"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
@@ -2889,7 +3204,7 @@
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
-      <c r="O28" s="40"/>
+      <c r="O28" s="25"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
